--- a/artifacts/COMPLEXE.xlsx
+++ b/artifacts/COMPLEXE.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lisez-moi" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hypotheses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historique" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formules" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modele" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="g_2026">'Hypotheses'!$C$3</definedName>
@@ -39,20 +40,20 @@
     <definedName name="gTerminal">'Hypotheses'!$C$25</definedName>
     <definedName name="margeTerminale">'Hypotheses'!$C$26</definedName>
     <definedName name="partMinos">'Hypotheses'!$C$27</definedName>
-    <definedName name="pub_ca">'Historique'!$B$3</definedName>
-    <definedName name="pub_margeBrute">'Historique'!$B$4</definedName>
-    <definedName name="pub_ebitda">'Historique'!$B$5</definedName>
-    <definedName name="pub_da">'Historique'!$B$6</definedName>
-    <definedName name="pub_ebit">'Historique'!$B$7</definedName>
-    <definedName name="pub_finNet">'Historique'!$B$8</definedName>
-    <definedName name="pub_avantImpot">'Historique'!$B$9</definedName>
-    <definedName name="pub_impot">'Historique'!$B$10</definedName>
-    <definedName name="pub_minoritaires">'Historique'!$B$11</definedName>
-    <definedName name="pub_net">'Historique'!$B$12</definedName>
-    <definedName name="impotRet">'Historique'!$D$26</definedName>
-    <definedName name="ajPub_ebitda">'Historique'!$B$33</definedName>
-    <definedName name="ajPub_ebit">'Historique'!$C$33</definedName>
-    <definedName name="ajPub_net">'Historique'!$D$33</definedName>
+    <definedName name="pub_ca">'Historique'!$F$3</definedName>
+    <definedName name="pub_margeBrute">'Historique'!$F$4</definedName>
+    <definedName name="pub_ebitda">'Historique'!$F$5</definedName>
+    <definedName name="pub_da">'Historique'!$F$6</definedName>
+    <definedName name="pub_ebit">'Historique'!$F$7</definedName>
+    <definedName name="pub_finNet">'Historique'!$F$8</definedName>
+    <definedName name="pub_avantImpot">'Historique'!$F$9</definedName>
+    <definedName name="pub_impot">'Historique'!$F$10</definedName>
+    <definedName name="pub_minoritaires">'Historique'!$F$11</definedName>
+    <definedName name="pub_net">'Historique'!$F$12</definedName>
+    <definedName name="impotRet">'Historique'!$D$28</definedName>
+    <definedName name="ajPub_ebitda">'Historique'!$B$35</definedName>
+    <definedName name="ajPub_ebit">'Historique'!$C$35</definedName>
+    <definedName name="ajPub_net">'Historique'!$D$35</definedName>
     <definedName name="CA_2025">'Modele'!$B$3</definedName>
     <definedName name="CA_2026">'Modele'!$C$3</definedName>
     <definedName name="CA_2027">'Modele'!$D$3</definedName>
@@ -168,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -185,9 +186,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -589,7 +595,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Complexe SA — moteur v1.0.0 — empreinte daaf23ea1ee0</t>
+          <t>Complexe SA — moteur v1.0.0 — empreinte b330e010bb69</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1548,7 +1554,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ECHELLE PUBLIEE 2025-FY — un modele unique, les barreaux non publies restent vides</t>
+          <t>ECHELLE PUBLIEE — un modele unique, les barreaux non publies restent vides</t>
         </is>
       </c>
       <c r="B1" s="4" t="n"/>
@@ -1566,7 +1572,27 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>publie</t>
+          <t>2021-FY</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>2022-FY</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>2023-FY</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>2024-FY</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>2025-FY</t>
         </is>
       </c>
     </row>
@@ -1577,6 +1603,18 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
+        <v>1740</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>1820</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>1940</v>
+      </c>
+      <c r="F3" s="11" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -1587,6 +1625,18 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
+        <v>957</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>1034</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>1067</v>
+      </c>
+      <c r="F4" s="11" t="n">
         <v>1100</v>
       </c>
     </row>
@@ -1597,6 +1647,18 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
+        <v>340</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>352</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>358</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>366</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>380</v>
       </c>
     </row>
@@ -1607,6 +1669,18 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
+        <v>-150</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>-162</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>-175</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>-183</v>
+      </c>
+      <c r="F6" s="11" t="n">
         <v>-190</v>
       </c>
     </row>
@@ -1619,6 +1693,18 @@
       <c r="B7" s="11" t="n">
         <v>190</v>
       </c>
+      <c r="C7" s="11" t="n">
+        <v>190</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>183</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>183</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -1627,6 +1713,18 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
+        <v>-30</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>-36</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>-42</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>-45</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>-48</v>
       </c>
     </row>
@@ -1637,6 +1735,18 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
+        <v>160</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>142</v>
       </c>
     </row>
@@ -1647,6 +1757,18 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
+        <v>-45.6</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>-43.9</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>-40.2</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>-39.3</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -1657,6 +1779,18 @@
         </is>
       </c>
       <c r="B11" s="11" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>-13.1</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>-22</v>
       </c>
     </row>
@@ -1667,414 +1801,448 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>80</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Taux d'impot effectif observe</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0.2850649350649351</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>0.2851063829787234</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0.2847826086956521</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0.2816901408450704</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>IDENTITES DE L'ECHELLE</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>ebitda + da = ebit</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="F17" s="14">
         <f>pub_ebitda+pub_da-pub_ebit</f>
         <v/>
       </c>
-      <c r="C15" s="2">
-        <f>IF(ABS(B15)&lt;=MAX(1,ABS(pub_ebit)*0.005),"OK","ECART")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="G17" s="2">
+        <f>IF(ABS(F17)&lt;=MAX(1,ABS(pub_ebit)*0.005),"OK","ECART")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>ebit + finNet = avantImpot</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="F18" s="14">
         <f>pub_ebit+pub_finNet-pub_avantImpot</f>
         <v/>
       </c>
-      <c r="C16" s="2">
-        <f>IF(ABS(B16)&lt;=MAX(1,ABS(pub_avantImpot)*0.005),"OK","ECART")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="G18" s="2">
+        <f>IF(ABS(F18)&lt;=MAX(1,ABS(pub_avantImpot)*0.005),"OK","ECART")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>avantImpot + impot + minoritaires = net</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="F19" s="14">
         <f>pub_avantImpot+pub_impot+pub_minoritaires-pub_net</f>
         <v/>
       </c>
-      <c r="C17" s="2">
-        <f>IF(ABS(B17)&lt;=MAX(1,ABS(pub_net)*0.005),"OK","ECART")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="G19" s="2">
+        <f>IF(ABS(F19)&lt;=MAX(1,ABS(pub_net)*0.005),"OK","ECART")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>RETRAITEMENTS — la table de l'emetteur, ligne a ligne</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>ligne</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>net</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>classe</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>origine</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>libelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>restructuration-plan-2025</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>oneOff</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>emetteur</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>One-off restructuring plan announced in 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>beta-ppa-amort</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>emetteur</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>Amortisation of intangibles from the Beta PPA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>gamma-ppa-amort</t>
+          <t>restructuration-plan-2025</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>recurrent</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr">
+        <v>45</v>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>oneOff</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>emetteur</t>
         </is>
       </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>Amortisation of intangibles from the Gamma PPA</t>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>One-off restructuring plan announced in 2025</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>dette-acquisition-interets</t>
+          <t>beta-ppa-amort</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
+        <v>42</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>recurrent</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>emetteur</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>Interest on the acquisition debt</t>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Amortisation of intangibles from the Beta PPA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>litige-provision-2025</t>
+          <t>gamma-ppa-amort</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>oneOff</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>omnium</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>Isolated litigation provision, not restated by the issuer</t>
+        <v>23</v>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>recurrent</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>emetteur</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Amortisation of intangibles from the Gamma PPA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>dette-acquisition-interets</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>recurrent</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>emetteur</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Interest on the acquisition debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>litige-provision-2025</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>oneOff</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>omnium</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Isolated litigation provision, not restated by the issuer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
           <t>impot sur retraitements</t>
         </is>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>-26</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>LES TROIS BASES — calculees, jamais saisies</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>base</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>ebit</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>net</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>moteur (net)</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>Omnium (publie + vrais one-offs)</t>
-        </is>
-      </c>
-      <c r="B30" s="11">
-        <f>pub_ebitda+SUMIF($E$21:$E$25,"oneOff",B$21:B$25)</f>
-        <v/>
-      </c>
-      <c r="C30" s="11">
-        <f>pub_ebit+SUMIF($E$21:$E$25,"oneOff",C$21:C$25)</f>
-        <v/>
-      </c>
-      <c r="D30" s="11">
-        <f>pub_net+SUMIF($E$21:$E$25,"oneOff",D$21:D$25)+impotRet*SUMIF($E$21:$E$25,"oneOff",$D$21:$D$25)/SUM($D$21:$D$25)</f>
-        <v/>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>135.73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>Ajuste du management (+ recurrents)</t>
-        </is>
-      </c>
-      <c r="B31" s="11">
-        <f>pub_ebitda+SUM(B$21:B$25)</f>
-        <v/>
-      </c>
-      <c r="C31" s="11">
-        <f>pub_ebit+SUM(C$21:C$25)</f>
-        <v/>
-      </c>
-      <c r="D31" s="11">
-        <f>pub_net+SUM(D$21:D$25)+impotRet</f>
-        <v/>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
+          <t>Omnium (publie + vrais one-offs)</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>pub_ebitda+SUMIF($E$23:$E$27,"oneOff",B$23:B$27)</f>
+        <v/>
+      </c>
+      <c r="C32" s="11">
+        <f>pub_ebit+SUMIF($E$23:$E$27,"oneOff",C$23:C$27)</f>
+        <v/>
+      </c>
+      <c r="D32" s="11">
+        <f>pub_net+SUMIF($E$23:$E$27,"oneOff",D$23:D$27)+impotRet*SUMIF($E$23:$E$27,"oneOff",$D$23:$D$27)/SUM($D$23:$D$27)</f>
+        <v/>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>135.73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Ajuste du management (+ recurrents)</t>
+        </is>
+      </c>
+      <c r="B33" s="11">
+        <f>pub_ebitda+SUM(B$23:B$27)</f>
+        <v/>
+      </c>
+      <c r="C33" s="11">
+        <f>pub_ebit+SUM(C$23:C$27)</f>
+        <v/>
+      </c>
+      <c r="D33" s="11">
+        <f>pub_net+SUM(D$23:D$27)+impotRet</f>
+        <v/>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
           <t>Coin = recurrents-deguises</t>
         </is>
       </c>
-      <c r="B32" s="11">
-        <f>SUMIF($E$21:$E$25,"recurrent",B$21:B$25)</f>
-        <v/>
-      </c>
-      <c r="C32" s="11">
-        <f>SUMIF($E$21:$E$25,"recurrent",C$21:C$25)</f>
-        <v/>
-      </c>
-      <c r="D32" s="11">
-        <f>SUMIF($E$21:$E$25,"recurrent",D$21:D$25)+impotRet*SUMIF($E$21:$E$25,"recurrent",$D$21:$D$25)/SUM($D$21:$D$25)</f>
-        <v/>
-      </c>
-      <c r="E32" s="12" t="n">
+      <c r="B34" s="11">
+        <f>SUMIF($E$23:$E$27,"recurrent",B$23:B$27)</f>
+        <v/>
+      </c>
+      <c r="C34" s="11">
+        <f>SUMIF($E$23:$E$27,"recurrent",C$23:C$27)</f>
+        <v/>
+      </c>
+      <c r="D34" s="11">
+        <f>SUMIF($E$23:$E$27,"recurrent",D$23:D$27)+impotRet*SUMIF($E$23:$E$27,"recurrent",$D$23:$D$27)/SUM($D$23:$D$27)</f>
+        <v/>
+      </c>
+      <c r="E34" s="13" t="n">
         <v>60.27</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>ajuste PUBLIE par la societe (cible de bouclage)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B35" s="11" t="n">
         <v>425</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C35" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D35" s="11" t="n">
         <v>178</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>BOUCLAGE</t>
         </is>
       </c>
-      <c r="B34" s="2">
-        <f>IF(ABS(B32-ajPub_ebitda)&lt;=MAX(1,ABS(ajPub_ebitda)*0.005),"OK","NE BOUCLE PAS")</f>
-        <v/>
-      </c>
-      <c r="C34" s="2">
-        <f>IF(ABS(C32-ajPub_ebit)&lt;=MAX(1,ABS(ajPub_ebit)*0.005),"OK","NE BOUCLE PAS")</f>
-        <v/>
-      </c>
-      <c r="D34" s="2">
-        <f>IF(ABS(D32-ajPub_net)&lt;=MAX(1,ABS(ajPub_net)*0.005),"OK","NE BOUCLE PAS")</f>
+      <c r="B36" s="2">
+        <f>IF(ABS(B34-ajPub_ebitda)&lt;=MAX(1,ABS(ajPub_ebitda)*0.005),"OK","NE BOUCLE PAS")</f>
+        <v/>
+      </c>
+      <c r="C36" s="2">
+        <f>IF(ABS(C34-ajPub_ebit)&lt;=MAX(1,ABS(ajPub_ebit)*0.005),"OK","NE BOUCLE PAS")</f>
+        <v/>
+      </c>
+      <c r="D36" s="2">
+        <f>IF(ABS(D34-ajPub_net)&lt;=MAX(1,ABS(ajPub_net)*0.005),"OK","NE BOUCLE PAS")</f>
         <v/>
       </c>
     </row>
@@ -2084,6 +2252,339 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FORMULES DU MODELE — l'ecriture du calcul, ligne par ligne</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ligne</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>calcul</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>formule posee sur 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>CA(n) = CA(n-1) x (1 + g_n)</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>'=B3*(1+g_2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>EBITDA(n) = CA(n) x marge_n</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>'=C3*C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>dotations hors PPA</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>dotHorsPPA(n) = dotHorsPPA(n-1) + CA(n-1) x capexRatio / dureeAmort</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>'=B7+B3*capexRatio/dureeAmort</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Dotations</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>dotations(n) = -( dotHorsPPA(n) + amortPPA(n) )</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>'=-(C7+C8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>EBIT(n) = EBITDA(n) + dotations(n)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>'=C6+C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Resultat financier (rang 2)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>resultatFinancier(n) = -detteBrute(n-1) x tauxDette + tresorerie(n-1) x tauxCash - detteLocative(n-1) x tauxLease   [rang 2]</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>'=-(B11*tauxDette)+B12*tauxCash-(B13*tauxLease)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Resultat avant impot</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>avantImpot(n) = EBIT(n) + resultatFinancier(n)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>'=C10+C14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Impot</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>impot(n) = -avantImpot(n) x tauxIS_n   [ou OVERRIDE declare]</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>'=-C15*C16</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Minoritaires</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>minoritaires(n) = partMinos x ( avantImpot(n) + impot(n) )</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>'=partMinos*(C15+C17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Resultat net</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>net(n) = avantImpot(n) + impot(n) + minoritaires(n)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>'=C15+C17+C18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Actions (millions)</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>actions(n) = actions(n-1) x (1 - rachatPct)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>'=B20*(1-rachatPct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>BPA</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>BPA(n) = net(n) / actions(n)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>'=C19/C20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Dividende verse</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>dividende(n) = net(n) x tauxDistrib</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>'=C19*tauxDistrib</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>OU LIRE LE RESTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Hypotheses</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>la valeur de chaque moteur, son rang de provenance et sa peremption</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Historique</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>l'echelle publiee de chaque exercice, ses identites, et les trois bases</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Modele</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>le deroule annee par annee ; la colonne de droite porte la valeur du moteur Python</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Controles</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>formule contre moteur, cellule a cellule</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>engine/model.py</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>la SOURCE des formules ci-dessus — le classeur n'en est que le miroir</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2130,34 +2631,34 @@
       <c r="B2" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="18" t="n">
         <v>2026</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="18" t="n">
         <v>2027</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="18" t="n">
         <v>2028</v>
       </c>
-      <c r="F2" s="15" t="n">
+      <c r="F2" s="18" t="n">
         <v>2029</v>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="18" t="n">
         <v>2030</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="13" t="n">
         <v>2027</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="13" t="n">
         <v>2028</v>
       </c>
-      <c r="L2" s="12" t="n">
+      <c r="L2" s="13" t="n">
         <v>2029</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M2" s="13" t="n">
         <v>2030</v>
       </c>
     </row>
@@ -2170,39 +2671,39 @@
       <c r="B3" s="11" t="n">
         <v>2000</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="19">
         <f>B3*(1+g_2026)</f>
         <v/>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="19">
         <f>C3*(1+g_2027)</f>
         <v/>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="19">
         <f>D3*(1+g_2028)</f>
         <v/>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="19">
         <f>E3*(1+g_2029)</f>
         <v/>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="19">
         <f>F3*(1+g_2030)</f>
         <v/>
       </c>
-      <c r="I3" s="17" t="n">
+      <c r="I3" s="20" t="n">
         <v>2060</v>
       </c>
-      <c r="J3" s="17" t="n">
+      <c r="J3" s="20" t="n">
         <v>1936.4</v>
       </c>
-      <c r="K3" s="17" t="n">
+      <c r="K3" s="20" t="n">
         <v>2013.856</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="20" t="n">
         <v>2104.4795</v>
       </c>
-      <c r="M3" s="17" t="n">
+      <c r="M3" s="20" t="n">
         <v>2199.1811</v>
       </c>
     </row>
@@ -2212,39 +2713,39 @@
           <t>Croissance</t>
         </is>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="21">
         <f>g_2026</f>
         <v/>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="21">
         <f>g_2027</f>
         <v/>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="21">
         <f>g_2028</f>
         <v/>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="21">
         <f>g_2029</f>
         <v/>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="21">
         <f>g_2030</f>
         <v/>
       </c>
-      <c r="I4" s="19" t="n">
+      <c r="I4" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="22" t="n">
         <v>-0.06</v>
       </c>
-      <c r="K4" s="19" t="n">
+      <c r="K4" s="22" t="n">
         <v>0.04</v>
       </c>
-      <c r="L4" s="19" t="n">
+      <c r="L4" s="22" t="n">
         <v>0.045</v>
       </c>
-      <c r="M4" s="19" t="n">
+      <c r="M4" s="22" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -2254,39 +2755,39 @@
           <t>Marge d'EBITDA</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="21">
         <f>marge_2026</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="21">
         <f>marge_2027</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="21">
         <f>marge_2028</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="21">
         <f>marge_2029</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="21">
         <f>marge_2030</f>
         <v/>
       </c>
-      <c r="I5" s="19" t="n">
+      <c r="I5" s="22" t="n">
         <v>0.192</v>
       </c>
-      <c r="J5" s="19" t="n">
+      <c r="J5" s="22" t="n">
         <v>0.15</v>
       </c>
-      <c r="K5" s="19" t="n">
+      <c r="K5" s="22" t="n">
         <v>0.178</v>
       </c>
-      <c r="L5" s="19" t="n">
+      <c r="L5" s="22" t="n">
         <v>0.19</v>
       </c>
-      <c r="M5" s="19" t="n">
+      <c r="M5" s="22" t="n">
         <v>0.195</v>
       </c>
     </row>
@@ -2299,39 +2800,39 @@
       <c r="B6" s="11" t="n">
         <v>380</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="19">
         <f>C3*C5</f>
         <v/>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="19">
         <f>D3*D5</f>
         <v/>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="19">
         <f>E3*E5</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="19">
         <f>F3*F5</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="19">
         <f>G3*G5</f>
         <v/>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="20" t="n">
         <v>395.52</v>
       </c>
-      <c r="J6" s="17" t="n">
+      <c r="J6" s="20" t="n">
         <v>290.46</v>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="K6" s="20" t="n">
         <v>358.4664</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="20" t="n">
         <v>399.8511</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="20" t="n">
         <v>428.8403</v>
       </c>
     </row>
@@ -2344,39 +2845,39 @@
       <c r="B7" s="11" t="n">
         <v>190</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="19">
         <f>B7+B3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="19">
         <f>C7+C3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="19">
         <f>D7+D3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="19">
         <f>E7+E3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="19">
         <f>F7+F3*capexRatio/dureeAmort</f>
         <v/>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="20" t="n">
         <v>202.2222</v>
       </c>
-      <c r="J7" s="17" t="n">
+      <c r="J7" s="20" t="n">
         <v>214.8111</v>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="K7" s="20" t="n">
         <v>226.6447</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="20" t="n">
         <v>238.9516</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="20" t="n">
         <v>251.8123</v>
       </c>
     </row>
@@ -2389,39 +2890,39 @@
       <c r="B8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="19">
         <f>73.0</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="19">
         <f>65.0</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="19">
         <f>50.0</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="19">
         <f>32.0</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="19">
         <f>22.0</f>
         <v/>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="20" t="n">
         <v>73</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J8" s="20" t="n">
         <v>65</v>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="K8" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="20" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2434,39 +2935,39 @@
       <c r="B9" s="11" t="n">
         <v>-190</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="19">
         <f>-(C7+C8)</f>
         <v/>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="19">
         <f>-(D7+D8)</f>
         <v/>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="19">
         <f>-(E7+E8)</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="19">
         <f>-(F7+F8)</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="19">
         <f>-(G7+G8)</f>
         <v/>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="20" t="n">
         <v>-275.2222</v>
       </c>
-      <c r="J9" s="17" t="n">
+      <c r="J9" s="20" t="n">
         <v>-279.8111</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="K9" s="20" t="n">
         <v>-276.6447</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="20" t="n">
         <v>-270.9516</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="20" t="n">
         <v>-273.8123</v>
       </c>
     </row>
@@ -2479,39 +2980,39 @@
       <c r="B10" s="11" t="n">
         <v>190</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="19">
         <f>C6+C9</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="19">
         <f>D6+D9</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="19">
         <f>E6+E9</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="19">
         <f>F6+F9</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="19">
         <f>G6+G9</f>
         <v/>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="20" t="n">
         <v>120.2978</v>
       </c>
-      <c r="J10" s="17" t="n">
+      <c r="J10" s="20" t="n">
         <v>10.6489</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="K10" s="20" t="n">
         <v>81.82170000000001</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="20" t="n">
         <v>128.8995</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="20" t="n">
         <v>155.028</v>
       </c>
     </row>
@@ -2524,23 +3025,23 @@
       <c r="B11" s="11" t="n">
         <v>1150</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="19">
         <f>B11</f>
         <v/>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="19">
         <f>C11</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="19">
         <f>D11</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="19">
         <f>E11</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="19">
         <f>F11</f>
         <v/>
       </c>
@@ -2554,23 +3055,23 @@
       <c r="B12" s="11" t="n">
         <v>180</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="19">
         <f>B12+C19-C22-B3*capexRatio-C9</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="19">
         <f>C12+D19-D22-C3*capexRatio-D9</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="19">
         <f>D12+E19-E22-D3*capexRatio-E9</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="19">
         <f>E12+F19-F22-E3*capexRatio-F9</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="19">
         <f>F12+G19-G22-F3*capexRatio-G9</f>
         <v/>
       </c>
@@ -2584,23 +3085,23 @@
       <c r="B13" s="11" t="n">
         <v>240</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="19">
         <f>B13</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="19">
         <f>C13</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="19">
         <f>D13</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="19">
         <f>E13</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="19">
         <f>F13</f>
         <v/>
       </c>
@@ -2614,39 +3115,39 @@
       <c r="B14" s="11" t="n">
         <v>-48</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="19">
         <f>-(B11*tauxDette)+B12*tauxCash-(B13*tauxLease)</f>
         <v/>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="19">
         <f>-(C11*tauxDette)+C12*tauxCash-(C13*tauxLease)</f>
         <v/>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="19">
         <f>-(D11*tauxDette)+D12*tauxCash-(D13*tauxLease)</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="19">
         <f>-(E11*tauxDette)+E12*tauxCash-(E13*tauxLease)</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="19">
         <f>-(F11*tauxDette)+F12*tauxCash-(F13*tauxLease)</f>
         <v/>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="20" t="n">
         <v>-61.08</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="20" t="n">
         <v>-57.6829</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="K14" s="20" t="n">
         <v>-55.2048</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="20" t="n">
         <v>-51.9559</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="20" t="n">
         <v>-48.5341</v>
       </c>
     </row>
@@ -2659,39 +3160,39 @@
       <c r="B15" s="11" t="n">
         <v>142</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="19">
         <f>C10+C14</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="19">
         <f>D10+D14</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="19">
         <f>E10+E14</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="19">
         <f>F10+F14</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="19">
         <f>G10+G14</f>
         <v/>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I15" s="20" t="n">
         <v>59.2178</v>
       </c>
-      <c r="J15" s="17" t="n">
+      <c r="J15" s="20" t="n">
         <v>-47.034</v>
       </c>
-      <c r="K15" s="17" t="n">
+      <c r="K15" s="20" t="n">
         <v>26.6169</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="20" t="n">
         <v>76.9436</v>
       </c>
-      <c r="M15" s="17" t="n">
+      <c r="M15" s="20" t="n">
         <v>106.494</v>
       </c>
     </row>
@@ -2701,39 +3202,39 @@
           <t>Taux d'impot applique</t>
         </is>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="21">
         <f>tauxIS_2026</f>
         <v/>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="21">
         <f>tauxIS_2027</f>
         <v/>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="21">
         <f>tauxIS_2028</f>
         <v/>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="21">
         <f>tauxIS_2029</f>
         <v/>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="21">
         <f>tauxIS_2030</f>
         <v/>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I16" s="22" t="n">
         <v>0.27</v>
       </c>
-      <c r="J16" s="19" t="n">
+      <c r="J16" s="22" t="n">
         <v>0.285</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="22" t="n">
         <v>0.285</v>
       </c>
-      <c r="L16" s="19" t="n">
+      <c r="L16" s="22" t="n">
         <v>0.285</v>
       </c>
-      <c r="M16" s="19" t="n">
+      <c r="M16" s="22" t="n">
         <v>0.285</v>
       </c>
     </row>
@@ -2746,38 +3247,38 @@
       <c r="B17" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="19">
         <f>-C15*C16</f>
         <v/>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="23" t="n">
         <v>-6</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="19">
         <f>-E15*E16</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="19">
         <f>-F15*F16</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="19">
         <f>-G15*G16</f>
         <v/>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I17" s="20" t="n">
         <v>-15.9888</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J17" s="20" t="n">
         <v>-6</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K17" s="20" t="n">
         <v>-7.5858</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="20" t="n">
         <v>-21.9289</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M17" s="20" t="n">
         <v>-30.3508</v>
       </c>
     </row>
@@ -2790,39 +3291,39 @@
       <c r="B18" s="11" t="n">
         <v>-22</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="19">
         <f>partMinos*(C15+C17)</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="19">
         <f>partMinos*(D15+D17)</f>
         <v/>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="19">
         <f>partMinos*(E15+E17)</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="19">
         <f>partMinos*(F15+F17)</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="19">
         <f>partMinos*(G15+G17)</f>
         <v/>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="I18" s="20" t="n">
         <v>-11.888</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="20" t="n">
         <v>14.5844</v>
       </c>
-      <c r="K18" s="17" t="n">
+      <c r="K18" s="20" t="n">
         <v>-5.2336</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="20" t="n">
         <v>-15.129</v>
       </c>
-      <c r="M18" s="17" t="n">
+      <c r="M18" s="20" t="n">
         <v>-20.9394</v>
       </c>
     </row>
@@ -2835,39 +3336,39 @@
       <c r="B19" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="19">
         <f>C15+C17+C18</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="19">
         <f>D15+D17+D18</f>
         <v/>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="19">
         <f>E15+E17+E18</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="19">
         <f>F15+F17+F18</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="19">
         <f>G15+G17+G18</f>
         <v/>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="20" t="n">
         <v>31.341</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="20" t="n">
         <v>-38.4497</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="K19" s="20" t="n">
         <v>13.7976</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="20" t="n">
         <v>39.8856</v>
       </c>
-      <c r="M19" s="17" t="n">
+      <c r="M19" s="20" t="n">
         <v>55.2038</v>
       </c>
     </row>
@@ -2877,42 +3378,42 @@
           <t>Actions (millions)</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="24" t="n">
         <v>64</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="25">
         <f>B20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="25">
         <f>C20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="25">
         <f>D20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="25">
         <f>E20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="25">
         <f>F20*(1-rachatPct)</f>
         <v/>
       </c>
-      <c r="I20" s="23" t="n">
+      <c r="I20" s="26" t="n">
         <v>63.488</v>
       </c>
-      <c r="J20" s="23" t="n">
+      <c r="J20" s="26" t="n">
         <v>62.9801</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="26" t="n">
         <v>62.4763</v>
       </c>
-      <c r="L20" s="23" t="n">
+      <c r="L20" s="26" t="n">
         <v>61.9764</v>
       </c>
-      <c r="M20" s="23" t="n">
+      <c r="M20" s="26" t="n">
         <v>61.4806</v>
       </c>
     </row>
@@ -2922,42 +3423,42 @@
           <t>BPA</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="24" t="n">
         <v>1.25</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="25">
         <f>C19/C20</f>
         <v/>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="25">
         <f>D19/D20</f>
         <v/>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="25">
         <f>E19/E20</f>
         <v/>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="25">
         <f>F19/F20</f>
         <v/>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="25">
         <f>G19/G20</f>
         <v/>
       </c>
-      <c r="I21" s="23" t="n">
+      <c r="I21" s="26" t="n">
         <v>0.4937</v>
       </c>
-      <c r="J21" s="23" t="n">
+      <c r="J21" s="26" t="n">
         <v>-0.6105</v>
       </c>
-      <c r="K21" s="23" t="n">
+      <c r="K21" s="26" t="n">
         <v>0.2208</v>
       </c>
-      <c r="L21" s="23" t="n">
+      <c r="L21" s="26" t="n">
         <v>0.6435999999999999</v>
       </c>
-      <c r="M21" s="23" t="n">
+      <c r="M21" s="26" t="n">
         <v>0.8979</v>
       </c>
     </row>
@@ -2967,39 +3468,39 @@
           <t>Dividende verse</t>
         </is>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="19">
         <f>C19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="19">
         <f>D19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="19">
         <f>E19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="19">
         <f>F19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="19">
         <f>G19*tauxDistrib</f>
         <v/>
       </c>
-      <c r="I22" s="17" t="n">
+      <c r="I22" s="20" t="n">
         <v>7.8353</v>
       </c>
-      <c r="J22" s="17" t="n">
+      <c r="J22" s="20" t="n">
         <v>-9.612399999999999</v>
       </c>
-      <c r="K22" s="17" t="n">
+      <c r="K22" s="20" t="n">
         <v>3.4494</v>
       </c>
-      <c r="L22" s="17" t="n">
+      <c r="L22" s="20" t="n">
         <v>9.971399999999999</v>
       </c>
-      <c r="M22" s="17" t="n">
+      <c r="M22" s="20" t="n">
         <v>13.801</v>
       </c>
     </row>
@@ -3011,128 +3512,128 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  croissance</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>implicite</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  marge</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>implicite</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>implicite</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  taux d'impot</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>guidance</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>override</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>normatif</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  resultat financier</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3144,7 +3645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3202,23 +3703,23 @@
           <t>Chiffre d'affaires</t>
         </is>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <f>IF(ABS(Modele!C3-Modele!I3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C3-Modele!I3,"0.00"))</f>
         <v/>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="15">
         <f>IF(ABS(Modele!D3-Modele!J3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D3-Modele!J3,"0.00"))</f>
         <v/>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="15">
         <f>IF(ABS(Modele!E3-Modele!K3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E3-Modele!K3,"0.00"))</f>
         <v/>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="15">
         <f>IF(ABS(Modele!F3-Modele!L3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F3-Modele!L3,"0.00"))</f>
         <v/>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="15">
         <f>IF(ABS(Modele!G3-Modele!M3)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G3-Modele!M3,"0.00"))</f>
         <v/>
       </c>
@@ -3229,23 +3730,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="15">
         <f>IF(ABS(Modele!C6-Modele!I6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C6-Modele!I6,"0.00"))</f>
         <v/>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="15">
         <f>IF(ABS(Modele!D6-Modele!J6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D6-Modele!J6,"0.00"))</f>
         <v/>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <f>IF(ABS(Modele!E6-Modele!K6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E6-Modele!K6,"0.00"))</f>
         <v/>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="15">
         <f>IF(ABS(Modele!F6-Modele!L6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F6-Modele!L6,"0.00"))</f>
         <v/>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="15">
         <f>IF(ABS(Modele!G6-Modele!M6)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G6-Modele!M6,"0.00"))</f>
         <v/>
       </c>
@@ -3256,23 +3757,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <f>IF(ABS(Modele!C10-Modele!I10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C10-Modele!I10,"0.00"))</f>
         <v/>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="15">
         <f>IF(ABS(Modele!D10-Modele!J10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D10-Modele!J10,"0.00"))</f>
         <v/>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="15">
         <f>IF(ABS(Modele!E10-Modele!K10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E10-Modele!K10,"0.00"))</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="15">
         <f>IF(ABS(Modele!F10-Modele!L10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F10-Modele!L10,"0.00"))</f>
         <v/>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="15">
         <f>IF(ABS(Modele!G10-Modele!M10)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G10-Modele!M10,"0.00"))</f>
         <v/>
       </c>
@@ -3283,23 +3784,23 @@
           <t>Resultat avant impot</t>
         </is>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="15">
         <f>IF(ABS(Modele!C15-Modele!I15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C15-Modele!I15,"0.00"))</f>
         <v/>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="15">
         <f>IF(ABS(Modele!D15-Modele!J15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D15-Modele!J15,"0.00"))</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <f>IF(ABS(Modele!E15-Modele!K15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E15-Modele!K15,"0.00"))</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <f>IF(ABS(Modele!F15-Modele!L15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F15-Modele!L15,"0.00"))</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <f>IF(ABS(Modele!G15-Modele!M15)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G15-Modele!M15,"0.00"))</f>
         <v/>
       </c>
@@ -3310,23 +3811,23 @@
           <t>Impot</t>
         </is>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <f>IF(ABS(Modele!C17-Modele!I17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C17-Modele!I17,"0.00"))</f>
         <v/>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="15">
         <f>IF(ABS(Modele!D17-Modele!J17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D17-Modele!J17,"0.00"))</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <f>IF(ABS(Modele!E17-Modele!K17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E17-Modele!K17,"0.00"))</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <f>IF(ABS(Modele!F17-Modele!L17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F17-Modele!L17,"0.00"))</f>
         <v/>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="15">
         <f>IF(ABS(Modele!G17-Modele!M17)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G17-Modele!M17,"0.00"))</f>
         <v/>
       </c>
@@ -3337,23 +3838,23 @@
           <t>Resultat net</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <f>IF(ABS(Modele!C19-Modele!I19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C19-Modele!I19,"0.00"))</f>
         <v/>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="15">
         <f>IF(ABS(Modele!D19-Modele!J19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D19-Modele!J19,"0.00"))</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <f>IF(ABS(Modele!E19-Modele!K19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E19-Modele!K19,"0.00"))</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="15">
         <f>IF(ABS(Modele!F19-Modele!L19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F19-Modele!L19,"0.00"))</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <f>IF(ABS(Modele!G19-Modele!M19)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G19-Modele!M19,"0.00"))</f>
         <v/>
       </c>
@@ -3364,23 +3865,23 @@
           <t>BPA</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="15">
         <f>IF(ABS(Modele!C21-Modele!I21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!C21-Modele!I21,"0.00"))</f>
         <v/>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <f>IF(ABS(Modele!D21-Modele!J21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!D21-Modele!J21,"0.00"))</f>
         <v/>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="15">
         <f>IF(ABS(Modele!E21-Modele!K21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!E21-Modele!K21,"0.00"))</f>
         <v/>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="15">
         <f>IF(ABS(Modele!F21-Modele!L21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!F21-Modele!L21,"0.00"))</f>
         <v/>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <f>IF(ABS(Modele!G21-Modele!M21)&lt;0.01,"OK","ECART "&amp;TEXT(Modele!G21-Modele!M21,"0.00"))</f>
         <v/>
       </c>
@@ -3398,7 +3899,7 @@
           <t>Aucune cellule orpheline (regle 5)</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="15">
         <f>IF(COUNTBLANK(Hypotheses!$C$3:$C$27)=0,"OK","MOTEUR MANQUANT")</f>
         <v/>
       </c>
@@ -3409,13 +3910,13 @@
           <t>Devise de reporting = devise de cotation (prop. 6)</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <f>IF(EXACT('Lisez-moi'!B10,'Lisez-moi'!B11),"OK","P/E INTERDIT SANS TAUX DATE")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Colonne 'moteur' de la feuille Modele = valeur produite par engine/model.py. Toute divergence est une erreur de traduction, pas une tolerance.</t>
         </is>

--- a/artifacts/COMPLEXE.xlsx
+++ b/artifacts/COMPLEXE.xlsx
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,6 +204,9 @@
     <xf numFmtId="4" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2590,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3637,6 +3640,688 @@
         <is>
           <t>2</t>
         </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>LES MEMES CELLULES, EN FORMULES — ce a quoi chaque chiffre fait reference</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ligne</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>cellule</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>2029</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Chiffre d'affaires</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>ligne 3</t>
+        </is>
+      </c>
+      <c r="C32" s="28">
+        <f>B3*(1+g_2026)</f>
+        <v/>
+      </c>
+      <c r="D32" s="28">
+        <f>C3*(1+g_2027)</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>D3*(1+g_2028)</f>
+        <v/>
+      </c>
+      <c r="F32" s="28">
+        <f>E3*(1+g_2029)</f>
+        <v/>
+      </c>
+      <c r="G32" s="28">
+        <f>F3*(1+g_2030)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Croissance</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>ligne 4</t>
+        </is>
+      </c>
+      <c r="C33" s="28">
+        <f>g_2026</f>
+        <v/>
+      </c>
+      <c r="D33" s="28">
+        <f>g_2027</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>g_2028</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>g_2029</f>
+        <v/>
+      </c>
+      <c r="G33" s="28">
+        <f>g_2030</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Marge d'EBITDA</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>ligne 5</t>
+        </is>
+      </c>
+      <c r="C34" s="28">
+        <f>marge_2026</f>
+        <v/>
+      </c>
+      <c r="D34" s="28">
+        <f>marge_2027</f>
+        <v/>
+      </c>
+      <c r="E34" s="28">
+        <f>marge_2028</f>
+        <v/>
+      </c>
+      <c r="F34" s="28">
+        <f>marge_2029</f>
+        <v/>
+      </c>
+      <c r="G34" s="28">
+        <f>marge_2030</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>ligne 6</t>
+        </is>
+      </c>
+      <c r="C35" s="28">
+        <f>C3*C5</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>D3*D5</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>E3*E5</f>
+        <v/>
+      </c>
+      <c r="F35" s="28">
+        <f>F3*F5</f>
+        <v/>
+      </c>
+      <c r="G35" s="28">
+        <f>G3*G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>dotations hors PPA</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>ligne 7</t>
+        </is>
+      </c>
+      <c r="C36" s="28">
+        <f>B7+B3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="D36" s="28">
+        <f>C7+C3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="E36" s="28">
+        <f>D7+D3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="F36" s="28">
+        <f>E7+E3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+      <c r="G36" s="28">
+        <f>F7+F3*capexRatio/dureeAmort</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>amortissement du PPA</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>ligne 8</t>
+        </is>
+      </c>
+      <c r="C37" s="28">
+        <f>73.0</f>
+        <v/>
+      </c>
+      <c r="D37" s="28">
+        <f>65.0</f>
+        <v/>
+      </c>
+      <c r="E37" s="28">
+        <f>50.0</f>
+        <v/>
+      </c>
+      <c r="F37" s="28">
+        <f>32.0</f>
+        <v/>
+      </c>
+      <c r="G37" s="28">
+        <f>22.0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Dotations</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>ligne 9</t>
+        </is>
+      </c>
+      <c r="C38" s="28">
+        <f>-(C7+C8)</f>
+        <v/>
+      </c>
+      <c r="D38" s="28">
+        <f>-(D7+D8)</f>
+        <v/>
+      </c>
+      <c r="E38" s="28">
+        <f>-(E7+E8)</f>
+        <v/>
+      </c>
+      <c r="F38" s="28">
+        <f>-(F7+F8)</f>
+        <v/>
+      </c>
+      <c r="G38" s="28">
+        <f>-(G7+G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>ligne 10</t>
+        </is>
+      </c>
+      <c r="C39" s="28">
+        <f>C6+C9</f>
+        <v/>
+      </c>
+      <c r="D39" s="28">
+        <f>D6+D9</f>
+        <v/>
+      </c>
+      <c r="E39" s="28">
+        <f>E6+E9</f>
+        <v/>
+      </c>
+      <c r="F39" s="28">
+        <f>F6+F9</f>
+        <v/>
+      </c>
+      <c r="G39" s="28">
+        <f>G6+G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Dette brute</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>ligne 11</t>
+        </is>
+      </c>
+      <c r="C40" s="28">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="D40" s="28">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="E40" s="28">
+        <f>D11</f>
+        <v/>
+      </c>
+      <c r="F40" s="28">
+        <f>E11</f>
+        <v/>
+      </c>
+      <c r="G40" s="28">
+        <f>F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Tresorerie</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>ligne 12</t>
+        </is>
+      </c>
+      <c r="C41" s="28">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="D41" s="28">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="E41" s="28">
+        <f>D12</f>
+        <v/>
+      </c>
+      <c r="F41" s="28">
+        <f>E12</f>
+        <v/>
+      </c>
+      <c r="G41" s="28">
+        <f>F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Dette locative</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>ligne 13</t>
+        </is>
+      </c>
+      <c r="C42" s="28">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="D42" s="28">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="E42" s="28">
+        <f>D13</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="G42" s="28">
+        <f>F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Resultat financier (rang 2)</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>ligne 14</t>
+        </is>
+      </c>
+      <c r="C43" s="28">
+        <f>-(B11*tauxDette)+B12*tauxCash-(B13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="D43" s="28">
+        <f>-(C11*tauxDette)+C12*tauxCash-(C13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="E43" s="28">
+        <f>-(D11*tauxDette)+D12*tauxCash-(D13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="F43" s="28">
+        <f>-(E11*tauxDette)+E12*tauxCash-(E13*tauxLease)</f>
+        <v/>
+      </c>
+      <c r="G43" s="28">
+        <f>-(F11*tauxDette)+F12*tauxCash-(F13*tauxLease)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Resultat avant impot</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>ligne 15</t>
+        </is>
+      </c>
+      <c r="C44" s="28">
+        <f>C10+C14</f>
+        <v/>
+      </c>
+      <c r="D44" s="28">
+        <f>D10+D14</f>
+        <v/>
+      </c>
+      <c r="E44" s="28">
+        <f>E10+E14</f>
+        <v/>
+      </c>
+      <c r="F44" s="28">
+        <f>F10+F14</f>
+        <v/>
+      </c>
+      <c r="G44" s="28">
+        <f>G10+G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Taux d'impot applique</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>ligne 16</t>
+        </is>
+      </c>
+      <c r="C45" s="28">
+        <f>tauxIS_2026</f>
+        <v/>
+      </c>
+      <c r="D45" s="28">
+        <f>tauxIS_2027</f>
+        <v/>
+      </c>
+      <c r="E45" s="28">
+        <f>tauxIS_2028</f>
+        <v/>
+      </c>
+      <c r="F45" s="28">
+        <f>tauxIS_2029</f>
+        <v/>
+      </c>
+      <c r="G45" s="28">
+        <f>tauxIS_2030</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Impot</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>ligne 17</t>
+        </is>
+      </c>
+      <c r="C46" s="28">
+        <f>-C15*C16</f>
+        <v/>
+      </c>
+      <c r="D46" s="28" t="inlineStr">
+        <is>
+          <t>valeur posee : -6.0</t>
+        </is>
+      </c>
+      <c r="E46" s="28">
+        <f>-E15*E16</f>
+        <v/>
+      </c>
+      <c r="F46" s="28">
+        <f>-F15*F16</f>
+        <v/>
+      </c>
+      <c r="G46" s="28">
+        <f>-G15*G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Minoritaires</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>ligne 18</t>
+        </is>
+      </c>
+      <c r="C47" s="28">
+        <f>partMinos*(C15+C17)</f>
+        <v/>
+      </c>
+      <c r="D47" s="28">
+        <f>partMinos*(D15+D17)</f>
+        <v/>
+      </c>
+      <c r="E47" s="28">
+        <f>partMinos*(E15+E17)</f>
+        <v/>
+      </c>
+      <c r="F47" s="28">
+        <f>partMinos*(F15+F17)</f>
+        <v/>
+      </c>
+      <c r="G47" s="28">
+        <f>partMinos*(G15+G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Resultat net</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>ligne 19</t>
+        </is>
+      </c>
+      <c r="C48" s="28">
+        <f>C15+C17+C18</f>
+        <v/>
+      </c>
+      <c r="D48" s="28">
+        <f>D15+D17+D18</f>
+        <v/>
+      </c>
+      <c r="E48" s="28">
+        <f>E15+E17+E18</f>
+        <v/>
+      </c>
+      <c r="F48" s="28">
+        <f>F15+F17+F18</f>
+        <v/>
+      </c>
+      <c r="G48" s="28">
+        <f>G15+G17+G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Actions (millions)</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>ligne 20</t>
+        </is>
+      </c>
+      <c r="C49" s="28">
+        <f>B20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="D49" s="28">
+        <f>C20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="E49" s="28">
+        <f>D20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="F49" s="28">
+        <f>E20*(1-rachatPct)</f>
+        <v/>
+      </c>
+      <c r="G49" s="28">
+        <f>F20*(1-rachatPct)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>BPA</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>ligne 21</t>
+        </is>
+      </c>
+      <c r="C50" s="28">
+        <f>C19/C20</f>
+        <v/>
+      </c>
+      <c r="D50" s="28">
+        <f>D19/D20</f>
+        <v/>
+      </c>
+      <c r="E50" s="28">
+        <f>E19/E20</f>
+        <v/>
+      </c>
+      <c r="F50" s="28">
+        <f>F19/F20</f>
+        <v/>
+      </c>
+      <c r="G50" s="28">
+        <f>G19/G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Dividende verse</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>ligne 22</t>
+        </is>
+      </c>
+      <c r="C51" s="28">
+        <f>C19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="D51" s="28">
+        <f>D19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="E51" s="28">
+        <f>E19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="F51" s="28">
+        <f>F19*tauxDistrib</f>
+        <v/>
+      </c>
+      <c r="G51" s="28">
+        <f>G19*tauxDistrib</f>
+        <v/>
       </c>
     </row>
   </sheetData>
